--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1894-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1894-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BB0DC0-4EA6-4F58-B05B-170347E35A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDF8FA1-D323-4EF0-8EEF-E62A7FFAB425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -963,7 +963,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1038,6 +1038,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1058,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1310,6 +1316,12 @@
     <xf numFmtId="3" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3007,7 +3019,7 @@
       </c>
       <c r="AB21" s="46">
         <f>SUM(K22:Y22)</f>
-        <v>64164</v>
+        <v>65164</v>
       </c>
       <c r="AC21" s="46">
         <f>SUM(K23:Y23)</f>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="AF21" s="46">
         <f>AB21-C21</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AG21" s="46">
         <f>AC21-D21</f>
@@ -3058,8 +3070,8 @@
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
-      <c r="K22" s="13">
-        <v>5744</v>
+      <c r="K22" s="85">
+        <v>6744</v>
       </c>
       <c r="L22" s="13">
         <v>9153</v>
@@ -4598,7 +4610,7 @@
       </c>
       <c r="AB42" s="70">
         <f>SUM(AB2:AB41)</f>
-        <v>959662</v>
+        <v>960662</v>
       </c>
       <c r="AC42" s="70">
         <f>SUM(AC2:AC41)</f>
@@ -4611,7 +4623,7 @@
       </c>
       <c r="AF42" s="70">
         <f>AB42-C42</f>
-        <v>-975</v>
+        <v>25</v>
       </c>
       <c r="AG42" s="70">
         <f>AC42-D42</f>
@@ -6583,11 +6595,11 @@
       </c>
       <c r="AB68" s="46">
         <f>SUM(K69:Y69)</f>
-        <v>21467</v>
+        <v>21767</v>
       </c>
       <c r="AC68" s="46">
         <f>SUM(K70:Y70)</f>
-        <v>15981</v>
+        <v>16281</v>
       </c>
       <c r="AD68" s="1"/>
       <c r="AE68" s="46">
@@ -6596,11 +6608,11 @@
       </c>
       <c r="AF68" s="46">
         <f>AB68-C68</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AG68" s="46">
         <f>AC68-D68</f>
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AH68" s="1"/>
       <c r="AI68" s="47">
@@ -6649,8 +6661,8 @@
       <c r="O69" s="13">
         <v>3068</v>
       </c>
-      <c r="P69" s="13">
-        <v>3522</v>
+      <c r="P69" s="85">
+        <v>3822</v>
       </c>
       <c r="Q69" s="13">
         <v>3529</v>
@@ -6706,8 +6718,8 @@
       <c r="O70" s="13">
         <v>2436</v>
       </c>
-      <c r="P70" s="13">
-        <v>2520</v>
+      <c r="P70" s="85">
+        <v>2820</v>
       </c>
       <c r="Q70" s="13">
         <v>2885</v>
@@ -7009,11 +7021,11 @@
       </c>
       <c r="AB74" s="70">
         <f>SUM(AB43:AB73)</f>
-        <v>383268</v>
+        <v>383568</v>
       </c>
       <c r="AC74" s="70">
         <f>SUM(AC43:AC73)</f>
-        <v>238286</v>
+        <v>238586</v>
       </c>
       <c r="AD74" s="1"/>
       <c r="AE74" s="70">
@@ -7022,11 +7034,11 @@
       </c>
       <c r="AF74" s="70">
         <f t="shared" si="1"/>
-        <v>-1442</v>
+        <v>-1142</v>
       </c>
       <c r="AG74" s="70">
         <f t="shared" si="1"/>
-        <v>-1523</v>
+        <v>-1223</v>
       </c>
       <c r="AH74" s="1"/>
       <c r="AI74" s="71">
@@ -8081,15 +8093,15 @@
       <c r="V88" s="38">
         <v>148335</v>
       </c>
-      <c r="W88" s="38">
-        <v>103593</v>
+      <c r="W88" s="85">
+        <v>108593</v>
       </c>
       <c r="X88" s="38"/>
       <c r="Y88" s="38"/>
       <c r="Z88" s="1"/>
       <c r="AA88" s="46">
         <f>SUM(K88:Y88)</f>
-        <v>1506063</v>
+        <v>1511063</v>
       </c>
       <c r="AB88" s="46">
         <f>SUM(K89:Y89)</f>
@@ -8102,7 +8114,7 @@
       <c r="AD88" s="1"/>
       <c r="AE88" s="46">
         <f>AA88-B88</f>
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="AF88" s="46">
         <f>AB88-C88</f>
@@ -9288,27 +9300,15 @@
         <f>SUM(K103:Y103)</f>
         <v>2240377</v>
       </c>
-      <c r="AB103" s="46">
-        <f>SUM(K104:Y104)</f>
-        <v>0</v>
-      </c>
-      <c r="AC103" s="46">
-        <f>SUM(K105:Y105)</f>
-        <v>0</v>
-      </c>
+      <c r="AB103" s="46"/>
+      <c r="AC103" s="46"/>
       <c r="AD103" s="1"/>
       <c r="AE103" s="46">
         <f>AA103-B103</f>
         <v>0</v>
       </c>
-      <c r="AF103" s="46">
-        <f>AB103-C103</f>
-        <v>-99514</v>
-      </c>
-      <c r="AG103" s="46">
-        <f>AC103-D103</f>
-        <v>-81672</v>
-      </c>
+      <c r="AF103" s="46"/>
+      <c r="AG103" s="46"/>
       <c r="AH103" s="1"/>
       <c r="AI103" s="47">
         <f>C103/B103*1000</f>
@@ -9469,8 +9469,8 @@
       <c r="B106" s="38">
         <v>1312802</v>
       </c>
-      <c r="C106" s="38">
-        <v>59586</v>
+      <c r="C106" s="85">
+        <v>61656</v>
       </c>
       <c r="D106" s="38">
         <v>47910</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="AF106" s="46">
         <f>AB106-C106</f>
-        <v>2070</v>
+        <v>0</v>
       </c>
       <c r="AG106" s="46">
         <f>AC106-D106</f>
@@ -9557,7 +9557,7 @@
       <c r="AH106" s="1"/>
       <c r="AI106" s="47">
         <f>C106/B106*1000</f>
-        <v>45.38841348504954</v>
+        <v>46.96519353261192</v>
       </c>
       <c r="AJ106" s="47">
         <f>D106/B106*1000</f>
@@ -9566,7 +9566,7 @@
       <c r="AK106" s="1"/>
       <c r="AL106" s="47">
         <f>AI106-H106</f>
-        <v>-1.1586514950458593E-2</v>
+        <v>1.5651935326119215</v>
       </c>
       <c r="AM106" s="47">
         <f>AJ106-I106</f>
@@ -9957,8 +9957,8 @@
       <c r="B112" s="38">
         <v>2617024</v>
       </c>
-      <c r="C112" s="38">
-        <v>111001</v>
+      <c r="C112" s="85">
+        <v>112002</v>
       </c>
       <c r="D112" s="38">
         <v>94098</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AF112" s="46">
         <f>AB112-C112</f>
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="AG112" s="46">
         <f>AC112-D112</f>
@@ -10053,7 +10053,7 @@
       <c r="AH112" s="1"/>
       <c r="AI112" s="47">
         <f>C112/B112*1000</f>
-        <v>42.414972121004624</v>
+        <v>42.797467657919839</v>
       </c>
       <c r="AJ112" s="47">
         <f>D112/B112*1000</f>
@@ -10062,7 +10062,7 @@
       <c r="AK112" s="1"/>
       <c r="AL112" s="47">
         <f>AI112-H112</f>
-        <v>1.4972121004625194E-2</v>
+        <v>0.39746765791984018</v>
       </c>
       <c r="AM112" s="47">
         <f>AJ112-I112</f>
@@ -11028,8 +11028,8 @@
       <c r="A125" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="B125" s="51">
-        <v>311617</v>
+      <c r="B125" s="85">
+        <v>371617</v>
       </c>
       <c r="C125" s="51">
         <v>14820</v>
@@ -11098,7 +11098,7 @@
       <c r="AD125" s="1"/>
       <c r="AE125" s="46">
         <f>AA125-B125</f>
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="AF125" s="46">
         <f>AB125-C125</f>
@@ -11111,20 +11111,20 @@
       <c r="AH125" s="1"/>
       <c r="AI125" s="47">
         <f>C125/B125*1000</f>
-        <v>47.55838096124409</v>
+        <v>39.879768686577847</v>
       </c>
       <c r="AJ125" s="47">
         <f>D125/B125*1000</f>
-        <v>43.746008722245577</v>
+        <v>36.682928929516144</v>
       </c>
       <c r="AK125" s="1"/>
       <c r="AL125" s="47">
         <f>AI125-H125</f>
-        <v>7.5583809612440902</v>
+        <v>-0.12023131342215265</v>
       </c>
       <c r="AM125" s="47">
         <f>AJ125-I125</f>
-        <v>7.1460087222455755</v>
+        <v>8.2928929516143057E-2</v>
       </c>
     </row>
     <row r="126" spans="1:39">
@@ -11532,8 +11532,8 @@
       <c r="O131" s="51">
         <v>187416</v>
       </c>
-      <c r="P131" s="51">
-        <v>166098</v>
+      <c r="P131" s="85">
+        <v>116098</v>
       </c>
       <c r="Q131" s="51">
         <v>133057</v>
@@ -11555,7 +11555,7 @@
       <c r="Z131" s="1"/>
       <c r="AA131" s="46">
         <f>SUM(K131:Y131)</f>
-        <v>1661570</v>
+        <v>1611570</v>
       </c>
       <c r="AB131" s="46">
         <f>SUM(K132:Y132)</f>
@@ -11568,7 +11568,7 @@
       <c r="AD131" s="1"/>
       <c r="AE131" s="46">
         <f>AA131-B131</f>
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AF131" s="46">
         <f>AB131-C131</f>
@@ -12038,8 +12038,8 @@
       <c r="W137" s="51">
         <v>228490</v>
       </c>
-      <c r="X137" s="51">
-        <v>222829</v>
+      <c r="X137" s="85">
+        <v>221829</v>
       </c>
       <c r="Y137" s="51">
         <v>185287</v>
@@ -12047,7 +12047,7 @@
       <c r="Z137" s="1"/>
       <c r="AA137" s="46">
         <f>SUM(K137:Y137)</f>
-        <v>3103588</v>
+        <v>3102588</v>
       </c>
       <c r="AB137" s="46">
         <f>SUM(K138:Y138)</f>
@@ -12060,7 +12060,7 @@
       <c r="AD137" s="1"/>
       <c r="AE137" s="46">
         <f>AA137-B137</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF137" s="46">
         <f>AB137-C137</f>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="AC143" s="46">
         <f>SUM(K145:Y145)</f>
-        <v>61844</v>
+        <v>63844</v>
       </c>
       <c r="AD143" s="1"/>
       <c r="AE143" s="46">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="AG143" s="46">
         <f>AC143-D143</f>
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AH143" s="1"/>
       <c r="AI143" s="47">
@@ -12681,8 +12681,8 @@
       <c r="T145" s="13">
         <v>6443</v>
       </c>
-      <c r="U145" s="13">
-        <v>3997</v>
+      <c r="U145" s="85">
+        <v>5997</v>
       </c>
       <c r="V145" s="13">
         <v>4841</v>
@@ -13028,8 +13028,8 @@
       <c r="K150" s="55">
         <v>131975</v>
       </c>
-      <c r="L150" s="55">
-        <v>154392</v>
+      <c r="L150" s="85">
+        <v>148992</v>
       </c>
       <c r="M150" s="55">
         <v>115365</v>
@@ -13059,7 +13059,7 @@
       <c r="Z150" s="1"/>
       <c r="AA150" s="46">
         <f>SUM(K150:Y150)</f>
-        <v>836776</v>
+        <v>831376</v>
       </c>
       <c r="AB150" s="46">
         <f>SUM(K151:Y151)</f>
@@ -13072,7 +13072,7 @@
       <c r="AD150" s="1"/>
       <c r="AE150" s="46">
         <f>AA150-B150</f>
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="AF150" s="46">
         <f>AB150-C150</f>
@@ -13681,8 +13681,8 @@
       <c r="A159" s="54" t="s">
         <v>159</v>
       </c>
-      <c r="B159" s="55">
-        <v>1480548</v>
+      <c r="B159" s="85">
+        <v>1563548</v>
       </c>
       <c r="C159" s="55">
         <v>79002</v>
@@ -13761,7 +13761,7 @@
       <c r="AD159" s="1"/>
       <c r="AE159" s="46">
         <f>AA159-B159</f>
-        <v>83000</v>
+        <v>0</v>
       </c>
       <c r="AF159" s="46">
         <f>AB159-C159</f>
@@ -13774,20 +13774,20 @@
       <c r="AH159" s="1"/>
       <c r="AI159" s="47">
         <f>C159/B159*1000</f>
-        <v>53.359972118431827</v>
+        <v>50.527390268798911</v>
       </c>
       <c r="AJ159" s="47">
         <f>D159/B159*1000</f>
-        <v>38.527626257304732</v>
+        <v>36.482410517617623</v>
       </c>
       <c r="AK159" s="1"/>
       <c r="AL159" s="47">
         <f>AI159-H159</f>
-        <v>5.9972118431829813E-2</v>
+        <v>-2.7726097312010864</v>
       </c>
       <c r="AM159" s="47">
         <f>AJ159-I159</f>
-        <v>2.7626257304731894E-2</v>
+        <v>-2.0175894823823768</v>
       </c>
     </row>
     <row r="160" spans="1:39">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AB162" s="46">
         <f>SUM(K163:Y163)</f>
-        <v>62148</v>
+        <v>63178</v>
       </c>
       <c r="AC162" s="46">
         <f>SUM(K164:Y164)</f>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="AF162" s="46">
         <f>AB162-C162</f>
-        <v>-1030</v>
+        <v>0</v>
       </c>
       <c r="AG162" s="46">
         <f>AC162-D162</f>
@@ -14044,8 +14044,8 @@
       <c r="H163" s="14"/>
       <c r="I163" s="14"/>
       <c r="J163" s="14"/>
-      <c r="K163" s="13">
-        <v>4389</v>
+      <c r="K163" s="85">
+        <v>5419</v>
       </c>
       <c r="L163" s="13">
         <v>15887</v>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="AB165" s="46">
         <f>SUM(K166:Y166)</f>
-        <v>141189</v>
+        <v>140589</v>
       </c>
       <c r="AC165" s="46">
         <f>SUM(K167:Y167)</f>
@@ -14241,7 +14241,7 @@
       </c>
       <c r="AF165" s="46">
         <f>AB165-C165</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="AG165" s="46">
         <f>AC165-D165</f>
@@ -14306,8 +14306,8 @@
       <c r="S166" s="13">
         <v>6698</v>
       </c>
-      <c r="T166" s="13">
-        <v>7866</v>
+      <c r="T166" s="85">
+        <v>7266</v>
       </c>
       <c r="U166" s="13">
         <v>11376</v>
@@ -15161,8 +15161,8 @@
       <c r="S177" s="59">
         <v>167676</v>
       </c>
-      <c r="T177" s="59">
-        <v>382138</v>
+      <c r="T177" s="85">
+        <v>392138</v>
       </c>
       <c r="U177" s="59">
         <v>241953</v>
@@ -15174,7 +15174,7 @@
       <c r="Z177" s="1"/>
       <c r="AA177" s="46">
         <f>SUM(K177:Y177)</f>
-        <v>2584840</v>
+        <v>2594840</v>
       </c>
       <c r="AB177" s="46">
         <f>SUM(K178:Y178)</f>
@@ -15187,7 +15187,7 @@
       <c r="AD177" s="1"/>
       <c r="AE177" s="46">
         <f>AA177-B177</f>
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="AF177" s="46">
         <f>AB177-C177</f>
@@ -15737,8 +15737,8 @@
       <c r="M185" s="59">
         <v>141470</v>
       </c>
-      <c r="N185" s="59">
-        <v>139192</v>
+      <c r="N185" s="85">
+        <v>143192</v>
       </c>
       <c r="O185" s="59">
         <v>134025</v>
@@ -15776,7 +15776,7 @@
       <c r="Z185" s="1"/>
       <c r="AA185" s="46">
         <f>SUM(K185:Y185)</f>
-        <v>2350023</v>
+        <v>2354023</v>
       </c>
       <c r="AB185" s="46">
         <f>SUM(K186:Y186)</f>
@@ -15784,12 +15784,12 @@
       </c>
       <c r="AC185" s="46">
         <f>SUM(K187:Y187)</f>
-        <v>71573</v>
+        <v>68578</v>
       </c>
       <c r="AD185" s="1"/>
       <c r="AE185" s="46">
         <f>AA185-B185</f>
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="AF185" s="46">
         <f>AB185-C185</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="AG185" s="46">
         <f>AC185-D185</f>
-        <v>2995</v>
+        <v>0</v>
       </c>
       <c r="AH185" s="1"/>
       <c r="AI185" s="47">
@@ -15913,8 +15913,8 @@
       <c r="M187" s="13">
         <v>4037</v>
       </c>
-      <c r="N187" s="13">
-        <v>5980</v>
+      <c r="N187" s="85">
+        <v>3985</v>
       </c>
       <c r="O187" s="13">
         <v>3777</v>
@@ -15928,8 +15928,8 @@
       <c r="R187" s="13">
         <v>5223</v>
       </c>
-      <c r="S187" s="13">
-        <v>5634</v>
+      <c r="S187" s="85">
+        <v>4634</v>
       </c>
       <c r="T187" s="13">
         <v>4712</v>
@@ -16240,28 +16240,28 @@
       <c r="Z191" s="1"/>
       <c r="AA191" s="70">
         <f>SUM(AA85:AA190)</f>
-        <v>67291144</v>
+        <v>67253744</v>
       </c>
       <c r="AB191" s="70">
         <f>SUM(AB85:AB190)</f>
-        <v>3126153</v>
+        <v>3126583</v>
       </c>
       <c r="AC191" s="70">
         <f>SUM(AC85:AC190)</f>
-        <v>2228790</v>
+        <v>2227795</v>
       </c>
       <c r="AD191" s="1"/>
       <c r="AE191" s="70">
         <f t="shared" ref="AE191:AG192" si="4">AA191-B191</f>
-        <v>162698</v>
+        <v>125298</v>
       </c>
       <c r="AF191" s="70">
         <f t="shared" si="4"/>
-        <v>-89280</v>
+        <v>-88850</v>
       </c>
       <c r="AG191" s="70">
         <f t="shared" si="4"/>
-        <v>-87247</v>
+        <v>-88242</v>
       </c>
       <c r="AH191" s="1"/>
       <c r="AI191" s="71">
@@ -16552,28 +16552,28 @@
       <c r="Z195" s="1"/>
       <c r="AA195" s="75">
         <f>SUM(AA42, AA84, AA74, AA191, AA192)</f>
-        <v>102768652</v>
+        <v>102731252</v>
       </c>
       <c r="AB195" s="75">
         <f>SUM(AB42, AB84, AB74, AB191, AB192)</f>
-        <v>4667639</v>
+        <v>4669369</v>
       </c>
       <c r="AC195" s="75">
         <f>SUM(AC42, AC84, AC74, AC191, AC192)</f>
-        <v>3220504</v>
+        <v>3219809</v>
       </c>
       <c r="AD195" s="1"/>
       <c r="AE195" s="70">
         <f t="shared" ref="AE195:AG196" si="5">AA195-B195</f>
-        <v>103811</v>
+        <v>66411</v>
       </c>
       <c r="AF195" s="70">
         <f t="shared" si="5"/>
-        <v>-91702</v>
+        <v>-89972</v>
       </c>
       <c r="AG195" s="70">
         <f t="shared" si="5"/>
-        <v>-88770</v>
+        <v>-89465</v>
       </c>
       <c r="AH195" s="1"/>
       <c r="AI195" s="71">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AB196" s="46">
         <f>SUM(K197:Y197)</f>
-        <v>21325</v>
+        <v>20325</v>
       </c>
       <c r="AC196" s="46">
         <f>SUM(K198:Y198)</f>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="AF196" s="46">
         <f t="shared" si="5"/>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG196" s="46">
         <f t="shared" si="5"/>
@@ -16720,8 +16720,8 @@
       <c r="N197" s="13">
         <v>7983</v>
       </c>
-      <c r="O197" s="13">
-        <v>3102</v>
+      <c r="O197" s="85">
+        <v>2102</v>
       </c>
       <c r="P197" s="13">
         <v>3896</v>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AC199" s="46">
         <f>SUM(K201:Y201)</f>
-        <v>10542</v>
+        <v>11542</v>
       </c>
       <c r="AD199" s="1"/>
       <c r="AE199" s="46">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="AG199" s="46">
         <f>AC199-D199</f>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AH199" s="1"/>
       <c r="AI199" s="47">
@@ -17004,8 +17004,8 @@
       <c r="R201" s="13">
         <v>1210</v>
       </c>
-      <c r="S201" s="13">
-        <v>996</v>
+      <c r="S201" s="85">
+        <v>1996</v>
       </c>
       <c r="T201" s="13"/>
       <c r="U201" s="13"/>
@@ -17366,8 +17366,8 @@
       <c r="N206" s="25">
         <v>195458</v>
       </c>
-      <c r="O206" s="25">
-        <v>221066</v>
+      <c r="O206" s="85">
+        <v>229166</v>
       </c>
       <c r="P206" s="25">
         <v>255710</v>
@@ -17388,11 +17388,11 @@
       <c r="Z206" s="1"/>
       <c r="AA206" s="46">
         <f>SUM(K206:Y206)</f>
-        <v>1644431</v>
+        <v>1652531</v>
       </c>
       <c r="AB206" s="46">
         <f>SUM(K207:Y207)</f>
-        <v>96504</v>
+        <v>98504</v>
       </c>
       <c r="AC206" s="46">
         <f>SUM(K208:Y208)</f>
@@ -17401,11 +17401,11 @@
       <c r="AD206" s="1"/>
       <c r="AE206" s="46">
         <f>AA206-B206</f>
-        <v>-8100</v>
+        <v>0</v>
       </c>
       <c r="AF206" s="46">
         <f>AB206-C206</f>
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AG206" s="46">
         <f>AC206-D206</f>
@@ -17461,8 +17461,8 @@
       <c r="P207" s="13">
         <v>12536</v>
       </c>
-      <c r="Q207" s="13">
-        <v>14822</v>
+      <c r="Q207" s="85">
+        <v>16822</v>
       </c>
       <c r="R207" s="13">
         <v>1932</v>
@@ -18209,8 +18209,8 @@
       <c r="A218" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="B218" s="25">
-        <v>899059</v>
+      <c r="B218" s="85">
+        <v>998059</v>
       </c>
       <c r="C218" s="25">
         <v>30730</v>
@@ -18283,7 +18283,7 @@
       <c r="AD218" s="1"/>
       <c r="AE218" s="46">
         <f>AA218-B218</f>
-        <v>99000</v>
+        <v>0</v>
       </c>
       <c r="AF218" s="46">
         <f>AB218-C218</f>
@@ -18296,20 +18296,20 @@
       <c r="AH218" s="1"/>
       <c r="AI218" s="47">
         <f>C218/B218*1000</f>
-        <v>34.180181723335174</v>
+        <v>30.789762929846834</v>
       </c>
       <c r="AJ218" s="47">
         <f>D218/B218*1000</f>
-        <v>22.902835075339883</v>
+        <v>20.631044858069512</v>
       </c>
       <c r="AK218" s="1"/>
       <c r="AL218" s="47">
         <f>AI218-H218</f>
-        <v>-1.3198182766648259</v>
+        <v>-4.7102370701531662</v>
       </c>
       <c r="AM218" s="47">
         <f>AJ218-I218</f>
-        <v>-0.89716492466011744</v>
+        <v>-3.1689551419304891</v>
       </c>
     </row>
     <row r="219" spans="1:39">
@@ -18766,28 +18766,28 @@
       <c r="Z225" s="1"/>
       <c r="AA225" s="70">
         <f>SUM(AA196:AA224)</f>
-        <v>8417627</v>
+        <v>8425727</v>
       </c>
       <c r="AB225" s="70">
         <f>SUM(AB196:AB224)</f>
-        <v>333912</v>
+        <v>334912</v>
       </c>
       <c r="AC225" s="70">
         <f>SUM(AC196:AC224)</f>
-        <v>212910</v>
+        <v>213910</v>
       </c>
       <c r="AD225" s="1"/>
       <c r="AE225" s="70">
         <f>AA225-B225</f>
-        <v>90900</v>
+        <v>99000</v>
       </c>
       <c r="AF225" s="70">
         <f>AB225-C225</f>
-        <v>-950</v>
+        <v>50</v>
       </c>
       <c r="AG225" s="70">
         <f>AC225-D225</f>
-        <v>-901</v>
+        <v>99</v>
       </c>
       <c r="AH225" s="1"/>
       <c r="AI225" s="71">
@@ -20976,8 +20976,8 @@
       <c r="K256" s="28">
         <v>305466</v>
       </c>
-      <c r="L256" s="28">
-        <v>258531</v>
+      <c r="L256" s="86">
+        <v>158531</v>
       </c>
       <c r="M256" s="28">
         <v>108941</v>
@@ -20999,7 +20999,7 @@
       <c r="Z256" s="1"/>
       <c r="AA256" s="46">
         <f>SUM(K256:Y256)</f>
-        <v>887468</v>
+        <v>787468</v>
       </c>
       <c r="AB256" s="46">
         <f>SUM(K257:Y257)</f>
@@ -21012,7 +21012,7 @@
       <c r="AD256" s="1"/>
       <c r="AE256" s="46">
         <f>AA256-B256</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AF256" s="46"/>
       <c r="AG256" s="46"/>
@@ -22241,7 +22241,7 @@
       <c r="Z275" s="1"/>
       <c r="AA275" s="70">
         <f>SUM(AA252:AA274)</f>
-        <v>6654495</v>
+        <v>6554495</v>
       </c>
       <c r="AB275" s="70">
         <f>SUM(AB252:AB274)</f>
@@ -22254,7 +22254,7 @@
       <c r="AD275" s="1"/>
       <c r="AE275" s="70">
         <f>AA275-B275</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AF275" s="70">
         <f>AB275-C275</f>
